--- a/input/EUROMODpolicySchedule.xlsx
+++ b/input/EUROMODpolicySchedule.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\labsim_Italy\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/EUROMODoutput/training/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F0610D-9867-49D9-9F5B-A4E2213BB68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A06C70-A646-D84E-8ACB-79662BA226A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="20400" tabRatio="993" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19720" tabRatio="993" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IT" sheetId="1" r:id="rId1"/>
-    <sheet name="UK" sheetId="2" r:id="rId2"/>
+    <sheet name="UK" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17436" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="37">
   <si>
     <t>Filename</t>
   </si>
@@ -37,27 +36,18 @@
     <t>Description</t>
   </si>
   <si>
-    <t>it_2016_std.txt</t>
-  </si>
-  <si>
     <t>2015</t>
   </si>
   <si>
     <t>2016</t>
   </si>
   <si>
-    <t>it_2015_std.txt</t>
-  </si>
-  <si>
     <t>2017</t>
   </si>
   <si>
     <t>2019</t>
   </si>
   <si>
-    <t>it_2020_web_std.txt</t>
-  </si>
-  <si>
     <t>2020</t>
   </si>
   <si>
@@ -76,24 +66,9 @@
     <t>2018</t>
   </si>
   <si>
-    <t>Policy for 2015</t>
-  </si>
-  <si>
-    <t>Policy for 2016</t>
-  </si>
-  <si>
-    <t>Policy for 2020 onwards</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>it_2020_web_std_v2.txt</t>
-  </si>
-  <si>
-    <t>uk_2015_e7_std.txt</t>
-  </si>
-  <si>
     <t>uk_2015_std.txt</t>
   </si>
   <si>
@@ -151,54 +126,6 @@
     <t>2024</t>
   </si>
   <si>
-    <t>uk_2021_10_std.txt</t>
-  </si>
-  <si>
-    <t>uk_2022_10_std.txt</t>
-  </si>
-  <si>
-    <t>uk_2023_10_std.txt</t>
-  </si>
-  <si>
-    <t>uk_2024_10_std.txt</t>
-  </si>
-  <si>
-    <t>uk_2010_std.txt</t>
-  </si>
-  <si>
-    <t>hscl_uk_2017_std.txt</t>
-  </si>
-  <si>
-    <t>hscl_uk_2018_std.txt</t>
-  </si>
-  <si>
-    <t>hscl_uk_2019_std.txt</t>
-  </si>
-  <si>
-    <t>hscl_uk_2020_std.txt</t>
-  </si>
-  <si>
-    <t>hscl_uk_2021_std.txt</t>
-  </si>
-  <si>
-    <t>hscl_uk_2022_std.txt</t>
-  </si>
-  <si>
-    <t>hscl_uk_2023_std.txt</t>
-  </si>
-  <si>
-    <t>hscl_uk_2024_std.txt</t>
-  </si>
-  <si>
-    <t>uk_2022_nohscl_std.txt</t>
-  </si>
-  <si>
-    <t>uk_2023_nohscl_std.txt</t>
-  </si>
-  <si>
-    <t>uk_2024_nohscl_std.txt</t>
-  </si>
-  <si>
     <t>uk_2025_std.txt</t>
   </si>
   <si>
@@ -209,19 +136,12 @@
   </si>
   <si>
     <t>2026</t>
-  </si>
-  <si>
-    <t>uk_2030_std.txt</t>
-  </si>
-  <si>
-    <t>2030</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -271,9 +191,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -311,7 +231,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -417,7 +337,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -559,180 +479,257 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5CC6207-DD24-427A-A7C5-E1B68985A6D0}">
+  <dimension ref="A1:AMK17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="17.85546875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="14.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="14.0" collapsed="true"/>
-    <col min="4" max="1026" width="8.7109375" collapsed="true"/>
+    <col min="1" max="1" width="17.83203125" customWidth="1" collapsed="1"/>
+    <col min="2" max="1025" width="9.1640625" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="D1" t="s" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5CC6207-DD24-427A-A7C5-E1B68985A6D0}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" customWidth="true" width="17.85546875" collapsed="true"/>
-    <col min="2" max="1025" width="9.140625" collapsed="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s" s="0">
+      <c r="C16" t="s">
         <v>34</v>
       </c>
-      <c r="D1" t="s" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>61</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>19</v>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
